--- a/budget_simple.xlsx
+++ b/budget_simple.xlsx
@@ -459,7 +459,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15.01.2025</t>
+          <t>15.01.2026</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -472,7 +472,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Бюджет 2025</t>
+          <t>Бюджет 2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>15.02.2026</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -502,7 +502,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Бюджет 2025</t>
+          <t>Бюджет 2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>15.03.2026</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -532,7 +532,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Бюджет 2025</t>
+          <t>Бюджет 2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15.01.2025</t>
+          <t>15.01.2026</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -562,7 +562,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Бюджет 2025</t>
+          <t>Бюджет 2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>15.02.2026</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -592,7 +592,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Бюджет 2025</t>
+          <t>Бюджет 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>15.03.2026</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Бюджет 2025</t>
+          <t>Бюджет 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
